--- a/tables/data_summaries.xlsx
+++ b/tables/data_summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/00042030/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D931CB6-3B8E-FF4B-896C-BBCB3EB0C480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F91BB8-9D09-CE41-8DC1-47DCD12EF687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="760" windowWidth="28680" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
   <si>
     <t>Table</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Microphytobenthos</t>
-  </si>
-  <si>
     <t>R_{mpb-g}</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>1 (KwinanaShelf)</t>
   </si>
   <si>
-    <t>Bulk PAR measured in OA and CS</t>
-  </si>
-  <si>
     <t>DWER-CSMOORING-MS9</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
     <t>WAMSI-WWMSP3-SEDDEP</t>
   </si>
   <si>
-    <t>Bulk PAR measured by turbidity loggers</t>
-  </si>
-  <si>
     <t>Dec 2022 - Dec 2023</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>Regular profile data used to compute integarted light attenuation</t>
   </si>
   <si>
-    <t>35 (XX regularly sampled sites)</t>
-  </si>
-  <si>
     <t>18 sites</t>
   </si>
   <si>
@@ -190,6 +178,30 @@
   </si>
   <si>
     <t>Attenuation (Kd)</t>
+  </si>
+  <si>
+    <t>35 (TBC regularly sampled sites)</t>
+  </si>
+  <si>
+    <t>1 (Mangles Bay)</t>
+  </si>
+  <si>
+    <t>Downwelling PAR installed at Woodman Point (NE Cockburn Sound)</t>
+  </si>
+  <si>
+    <t>Downwelling PAR installed on Mangles Bay mooring (SW Cockburn Sound)</t>
+  </si>
+  <si>
+    <t>Bulk PAR measured by turbidity loggers in CS and OA locations</t>
+  </si>
+  <si>
+    <t>Bulk PAR measured in OA and CS locations for ~ 5 intensive deployments</t>
+  </si>
+  <si>
+    <t>Turbidity</t>
+  </si>
+  <si>
+    <t>TSS</t>
   </si>
 </sst>
 </file>
@@ -616,7 +628,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
@@ -632,19 +644,19 @@
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -652,37 +664,41 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>34</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -690,22 +706,22 @@
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -713,19 +729,19 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E5" s="7">
         <v>6</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G5" s="7"/>
     </row>
@@ -734,66 +750,64 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7">
-        <v>10</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="7">
-        <v>10</v>
-      </c>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="7">
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -801,80 +815,76 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="7">
-        <v>50</v>
-      </c>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
-        <v>1.8</v>
-      </c>
+      <c r="F10" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>9</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>10</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>4</v>
@@ -882,19 +892,22 @@
       <c r="F12" s="13">
         <v>0.6</v>
       </c>
+      <c r="G12" s="13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>12</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>4</v>
@@ -902,19 +915,22 @@
       <c r="F13" s="13">
         <v>0.2</v>
       </c>
+      <c r="G13" s="13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>24</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>4</v>
@@ -922,16 +938,19 @@
       <c r="F14" s="13">
         <v>0.2</v>
       </c>
+      <c r="G14" s="13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>5</v>
@@ -942,39 +961,45 @@
       <c r="F15" s="13">
         <v>10</v>
       </c>
+      <c r="G15" s="13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>16</v>
       </c>
       <c r="F16" s="13">
         <v>1500</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G16" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C17" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>18</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>2</v>
@@ -982,19 +1007,22 @@
       <c r="F17" s="13">
         <v>1.2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G17" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>19</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>20</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>2</v>
@@ -1002,25 +1030,31 @@
       <c r="F18" s="13">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G18" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>2</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/tables/data_summaries.xlsx
+++ b/tables/data_summaries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/00042030/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F91BB8-9D09-CE41-8DC1-47DCD12EF687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62225FD1-86FE-7440-96C6-8212B14324B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="760" windowWidth="28680" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
   <si>
     <t>Table</t>
   </si>
@@ -114,21 +114,12 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>Spectral</t>
-  </si>
-  <si>
     <t>WAMSI-WWMSP2-MS9</t>
   </si>
   <si>
     <t>Nov 2022 - July 2023</t>
   </si>
   <si>
-    <t>non-shaded data-set @ ~8m deep.</t>
-  </si>
-  <si>
     <t>WAMSI-WWMSP5-WQ</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>Attenuation (Kd)</t>
   </si>
   <si>
-    <t>35 (TBC regularly sampled sites)</t>
-  </si>
-  <si>
     <t>1 (Mangles Bay)</t>
   </si>
   <si>
@@ -202,6 +190,21 @@
   </si>
   <si>
     <t>TSS</t>
+  </si>
+  <si>
+    <t>TBC</t>
+  </si>
+  <si>
+    <t>PAR (below water)</t>
+  </si>
+  <si>
+    <t>Spectrally-resolved data</t>
+  </si>
+  <si>
+    <t>35 (...TBC... regularly sampled sites)</t>
+  </si>
+  <si>
+    <t>non-shaded data-set @ ~8m deep</t>
   </si>
 </sst>
 </file>
@@ -329,7 +332,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -343,6 +345,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,8 +635,8 @@
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
     <col min="6" max="6" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.83203125" customWidth="1"/>
   </cols>
@@ -652,10 +657,10 @@
       <c r="E1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -664,64 +669,64 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>33</v>
+      <c r="E4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -729,85 +734,85 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="7">
+        <v>51</v>
+      </c>
+      <c r="E5" s="13">
         <v>6</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="7"/>
+      <c r="F5" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>52</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>33</v>
+      <c r="G8" s="13" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -815,245 +820,245 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="13"/>
     </row>
     <row r="11" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="7"/>
+      <c r="G11" s="13"/>
     </row>
     <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="A12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>0.6</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="A13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>0.2</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="A14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>0.2</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="A15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>10</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="A16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>1500</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="A17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>1.2</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="A18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="12">
         <v>20</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="A19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="12" t="s">
         <v>24</v>
       </c>
     </row>

--- a/tables/data_summaries.xlsx
+++ b/tables/data_summaries.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/00042030/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62225FD1-86FE-7440-96C6-8212B14324B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB45EDE-0540-8A49-84D4-EC85EDE76129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="760" windowWidth="28680" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="csiem_data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="73">
   <si>
     <t>Table</t>
   </si>
@@ -138,9 +139,6 @@
     <t>Bulk PAR computed from MS9 spectral data</t>
   </si>
   <si>
-    <t>4 sites</t>
-  </si>
-  <si>
     <t>PAR (above water)</t>
   </si>
   <si>
@@ -159,9 +157,6 @@
     <t>WAMSI-WWMSP3-CTD</t>
   </si>
   <si>
-    <t>Regular profile data used to compute integarted light attenuation</t>
-  </si>
-  <si>
     <t>18 sites</t>
   </si>
   <si>
@@ -171,9 +166,6 @@
     <t>Attenuation (Kd)</t>
   </si>
   <si>
-    <t>1 (Mangles Bay)</t>
-  </si>
-  <si>
     <t>Downwelling PAR installed at Woodman Point (NE Cockburn Sound)</t>
   </si>
   <si>
@@ -192,19 +184,67 @@
     <t>TSS</t>
   </si>
   <si>
-    <t>TBC</t>
-  </si>
-  <si>
     <t>PAR (below water)</t>
   </si>
   <si>
     <t>Spectrally-resolved data</t>
   </si>
   <si>
-    <t>35 (...TBC... regularly sampled sites)</t>
-  </si>
-  <si>
     <t>non-shaded data-set @ ~8m deep</t>
+  </si>
+  <si>
+    <t>DWER-CSMOORING-MS9D</t>
+  </si>
+  <si>
+    <t>Aug 2023 - Jan 2025</t>
+  </si>
+  <si>
+    <t>Wavelength specific and bulk-PAR $K_d$ estimated for a range of environment conditions</t>
+  </si>
+  <si>
+    <t>Seven paired MS9 deployments used to compute high-frequency light attenuation</t>
+  </si>
+  <si>
+    <t>1 (CS86, near Mangles Bay)</t>
+  </si>
+  <si>
+    <t>Regular profile data used to compute depth-integrated light attenuation</t>
+  </si>
+  <si>
+    <t>Dec 1984 - Jun 2023</t>
+  </si>
+  <si>
+    <t>33 (18 regularly sampled sites)</t>
+  </si>
+  <si>
+    <t>8 (4 deep and 4 shallow)</t>
+  </si>
+  <si>
+    <t>Dec 2021 - Dec 2024</t>
+  </si>
+  <si>
+    <t>4 sites were profiling for ~ 12 months, reconfigured data now has 6 bottom sensors</t>
+  </si>
+  <si>
+    <t>Nov 2021 - Aug 2022</t>
+  </si>
+  <si>
+    <t>6 MGL loggers with hourly data</t>
+  </si>
+  <si>
+    <t>4 deployment windows using miniPAR loggers</t>
+  </si>
+  <si>
+    <t>6 sites</t>
+  </si>
+  <si>
+    <t>Feb 2022 - Dec 2024</t>
+  </si>
+  <si>
+    <t>note attenuation in raw data converted by x2.3 to shift from log10 to ln</t>
+  </si>
+  <si>
+    <t>2 (Mangles Bay and Boat Club)</t>
   </si>
 </sst>
 </file>
@@ -629,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -669,13 +709,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="D2" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>34</v>
@@ -683,35 +723,39 @@
       <c r="F2" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="13"/>
+        <v>70</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>29</v>
@@ -726,7 +770,7 @@
         <v>30</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -734,49 +778,53 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="13">
-        <v>6</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="13"/>
+      <c r="G5" s="13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="13"/>
+        <v>66</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>35</v>
@@ -785,19 +833,21 @@
         <v>36</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="13"/>
+        <v>64</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>29</v>
@@ -805,14 +855,14 @@
       <c r="D8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="13">
-        <v>1</v>
+      <c r="E8" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>30</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -820,7 +870,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>35</v>
@@ -829,96 +879,102 @@
         <v>36</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="13"/>
+        <v>64</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="13"/>
+        <v>61</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="F11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="G11" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="13"/>
-    </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>24</v>
+      <c r="C12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="12">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="12" t="s">
         <v>24</v>
@@ -926,16 +982,16 @@
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>4</v>
@@ -949,22 +1005,22 @@
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="12">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>24</v>
@@ -972,22 +1028,22 @@
     </row>
     <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F16" s="12">
-        <v>1500</v>
+        <v>10</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>24</v>
@@ -995,22 +1051,22 @@
     </row>
     <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F17" s="12">
-        <v>1.2</v>
+        <v>1500</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>24</v>
@@ -1018,47 +1074,540 @@
     </row>
     <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>2</v>
       </c>
       <c r="F18" s="12">
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>24</v>
+      <c r="F19" s="12">
+        <v>20</v>
       </c>
       <c r="G19" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A9BC1D-FCDF-A741-A807-960D56DE7690}">
+  <dimension ref="A2:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="144" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="12">
+        <v>10</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="12">
+        <v>1500</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="12">
+        <v>20</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+      <c r="A21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>24</v>
       </c>
     </row>
